--- a/402/402_12.xlsx
+++ b/402/402_12.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Statistics\4th year\411(practical by Anika)\Session 2 (402)\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F277F6-98BC-4D51-AD1B-BF19D7086356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{B7CABBBB-0AB7-44A4-B7B1-352B71EF2D6D}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19140" windowHeight="10140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
   <si>
     <t>Place of</t>
   </si>
@@ -73,13 +67,19 @@
   </si>
   <si>
     <t>ER</t>
+  </si>
+  <si>
+    <t>In Migration</t>
+  </si>
+  <si>
+    <t>Out Migration</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,14 +112,6 @@
       <color rgb="FF002060"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,9 +151,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -175,6 +164,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -483,46 +475,44 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE5295E-A515-4D4D-97EC-825488745BEF}">
-  <dimension ref="B4:O19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B4:O23"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="8.7109375" style="5"/>
     <col min="2" max="2" width="13" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="11.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.7265625" style="5"/>
+    <col min="11" max="11" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:15" ht="15" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -538,31 +528,31 @@
       <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8" t="s">
+      <c r="G5" s="11"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="10"/>
-    </row>
-    <row r="6" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="O5" s="9"/>
+    </row>
+    <row r="6" spans="2:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
@@ -582,36 +572,36 @@
         <f>SUM(C6:F6)</f>
         <v>18531963</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f>G6-C6</f>
         <v>167988</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <f>(H6/G6)*1000</f>
         <v>9.0647709581548384</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>432585</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <f>(J6/G6)*1000</f>
         <v>23.34264319435561</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <f>I6-K6</f>
         <v>-14.277872236200771</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <f>I6+K6</f>
         <v>32.407414152510448</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
         <f>ABS(L6/M6)*100</f>
         <v>44.057425158973174</v>
       </c>
-      <c r="O6" s="10"/>
-    </row>
-    <row r="7" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="O6" s="9"/>
+    </row>
+    <row r="7" spans="2:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
@@ -631,36 +621,36 @@
         <f t="shared" ref="G7:G10" si="0">SUM(C7:F7)</f>
         <v>21209828</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f>G7-D7</f>
         <v>489928</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <f>(H7/G7)*1000</f>
         <v>23.099102925304251</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>329486</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
         <f>(J7/G7)*1000</f>
         <v>15.534590850996057</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <f t="shared" ref="L7:L9" si="1">I7-K7</f>
         <v>7.5645120743081939</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="9">
         <f t="shared" ref="M7:M9" si="2">I7+K7</f>
         <v>38.633693776300305</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="9">
         <f t="shared" ref="N7:N9" si="3">ABS(L7/M7)*100</f>
         <v>19.580090161993819</v>
       </c>
-      <c r="O7" s="10"/>
-    </row>
-    <row r="8" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="O7" s="9"/>
+    </row>
+    <row r="8" spans="2:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
@@ -680,36 +670,36 @@
         <f t="shared" si="0"/>
         <v>13843633</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f>G8-E8</f>
         <v>124107</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <f>(H8/G8)*1000</f>
         <v>8.9649154958095174</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <v>160648</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="9">
         <f>(J8/G8)*1000</f>
         <v>11.604468277944092</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <f t="shared" si="1"/>
         <v>-2.6395527821345741</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="9">
         <f t="shared" si="2"/>
         <v>20.569383773753607</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="9">
         <f t="shared" si="3"/>
         <v>12.832434900177347</v>
       </c>
-      <c r="O8" s="10"/>
-    </row>
-    <row r="9" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="O8" s="9"/>
+    </row>
+    <row r="9" spans="2:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
@@ -729,36 +719,36 @@
         <f t="shared" si="0"/>
         <v>17012103</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f>G9-F9</f>
         <v>250978</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <f>(H9/G9)*1000</f>
         <v>14.752908561628153</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>110282</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <f>(J9/G9)*1000</f>
         <v>6.4825612682923444</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <f t="shared" si="1"/>
         <v>8.27034729333581</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="9">
         <f t="shared" si="2"/>
         <v>21.235469829920497</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="9">
         <f t="shared" si="3"/>
         <v>38.945911531860716</v>
       </c>
-      <c r="O9" s="10"/>
-    </row>
-    <row r="10" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="O9" s="9"/>
+    </row>
+    <row r="10" spans="2:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
@@ -782,21 +772,21 @@
         <f t="shared" si="0"/>
         <v>70597527</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <f>SUM(H6:H9)</f>
         <v>1033001</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10">
         <v>1033001</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-    </row>
-    <row r="11" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+    </row>
+    <row r="11" spans="2:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
@@ -820,46 +810,333 @@
         <f>SUM(C11:F11)</f>
         <v>1033001</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-    </row>
-    <row r="12" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+    </row>
+    <row r="12" spans="2:15" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B12" s="2"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-    </row>
-    <row r="16" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="4:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="4:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="4:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+    </row>
+    <row r="16" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1">
+        <v>18363975</v>
+      </c>
+      <c r="D18" s="1">
+        <v>134513</v>
+      </c>
+      <c r="E18" s="1">
+        <v>21809</v>
+      </c>
+      <c r="F18" s="1">
+        <v>11666</v>
+      </c>
+      <c r="G18" s="5">
+        <f>SUM(C18:F18)</f>
+        <v>18531963</v>
+      </c>
+      <c r="H18" s="5">
+        <f>G18-C18</f>
+        <v>167988</v>
+      </c>
+      <c r="I18" s="5">
+        <f>C23</f>
+        <v>432585</v>
+      </c>
+      <c r="J18" s="5">
+        <f>H18/G18*1000</f>
+        <v>9.0647709581548384</v>
+      </c>
+      <c r="K18" s="5">
+        <f>I18/G18*1000</f>
+        <v>23.34264319435561</v>
+      </c>
+      <c r="L18" s="5">
+        <f>J18-K18</f>
+        <v>-14.277872236200771</v>
+      </c>
+      <c r="M18" s="5">
+        <f>J18+K18</f>
+        <v>32.407414152510448</v>
+      </c>
+      <c r="N18" s="5">
+        <f>ABS(L18/M18)*100</f>
+        <v>44.057425158973174</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1">
+        <v>311324</v>
+      </c>
+      <c r="D19" s="1">
+        <v>20719900</v>
+      </c>
+      <c r="E19" s="1">
+        <v>112689</v>
+      </c>
+      <c r="F19" s="1">
+        <v>65915</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" ref="G19:G22" si="5">SUM(C19:F19)</f>
+        <v>21209828</v>
+      </c>
+      <c r="H19" s="5">
+        <f>G19-D19</f>
+        <v>489928</v>
+      </c>
+      <c r="I19" s="5">
+        <f>D23</f>
+        <v>329486</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" ref="J19:J21" si="6">H19/G19*1000</f>
+        <v>23.099102925304251</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" ref="K19:K21" si="7">I19/G19*1000</f>
+        <v>15.534590850996057</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" ref="L19:L21" si="8">J19-K19</f>
+        <v>7.5645120743081939</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" ref="M19:M23" si="9">J19+K19</f>
+        <v>38.633693776300305</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" ref="N19:N23" si="10">ABS(L19/M19)*100</f>
+        <v>19.580090161993819</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1">
+        <v>75784</v>
+      </c>
+      <c r="D20" s="1">
+        <v>15622</v>
+      </c>
+      <c r="E20" s="1">
+        <v>13719526</v>
+      </c>
+      <c r="F20" s="1">
+        <v>32701</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="5"/>
+        <v>13843633</v>
+      </c>
+      <c r="H20" s="5">
+        <f>G20-E20</f>
+        <v>124107</v>
+      </c>
+      <c r="I20" s="5">
+        <f>E23</f>
+        <v>160648</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="6"/>
+        <v>8.9649154958095174</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" si="7"/>
+        <v>11.604468277944092</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="8"/>
+        <v>-2.6395527821345741</v>
+      </c>
+      <c r="M20" s="5">
+        <f t="shared" si="9"/>
+        <v>20.569383773753607</v>
+      </c>
+      <c r="N20" s="5">
+        <f t="shared" si="10"/>
+        <v>12.832434900177347</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45477</v>
+      </c>
+      <c r="D21" s="1">
+        <v>179351</v>
+      </c>
+      <c r="E21" s="1">
+        <v>26150</v>
+      </c>
+      <c r="F21" s="1">
+        <v>16761125</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" si="5"/>
+        <v>17012103</v>
+      </c>
+      <c r="H21" s="5">
+        <f>G21-F21</f>
+        <v>250978</v>
+      </c>
+      <c r="I21" s="5">
+        <f>F23</f>
+        <v>110282</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="6"/>
+        <v>14.752908561628153</v>
+      </c>
+      <c r="K21" s="5">
+        <f t="shared" si="7"/>
+        <v>6.4825612682923444</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="8"/>
+        <v>8.27034729333581</v>
+      </c>
+      <c r="M21" s="5">
+        <f t="shared" si="9"/>
+        <v>21.235469829920497</v>
+      </c>
+      <c r="N21" s="5">
+        <f t="shared" si="10"/>
+        <v>38.945911531860716</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="5">
+        <f>SUM(C18:C21)</f>
+        <v>18796560</v>
+      </c>
+      <c r="D22" s="5">
+        <f t="shared" ref="D22:G22" si="11">SUM(D18:D21)</f>
+        <v>21049386</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="11"/>
+        <v>13880174</v>
+      </c>
+      <c r="F22" s="5">
+        <f t="shared" si="11"/>
+        <v>16871407</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="11"/>
+        <v>70597527</v>
+      </c>
+      <c r="H22" s="5">
+        <f>SUM(H18:H21)</f>
+        <v>1033001</v>
+      </c>
+      <c r="I22" s="5">
+        <f>SUM(I18:I21)</f>
+        <v>1033001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="5">
+        <f>C22-C18</f>
+        <v>432585</v>
+      </c>
+      <c r="D23" s="5">
+        <f>D22-D19</f>
+        <v>329486</v>
+      </c>
+      <c r="E23" s="5">
+        <f>E22-E20</f>
+        <v>160648</v>
+      </c>
+      <c r="F23" s="5">
+        <f>F22-F21</f>
+        <v>110282</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
